--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA67B3D8-DBE8-43B6-990F-CEB34D43EDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C6F127-64A8-4683-886C-F592279544ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
